--- a/refs/heads/main/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/main/StructureDefinition-AppointmentLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -408,33 +408,55 @@
     <t>Appointment.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedioNotificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MedioNotificacion}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Contactado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Contactado}
+</t>
+  </si>
+  <si>
+    <t>Appointment.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Appointment.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -442,6 +464,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -498,17 +523,13 @@
     <t>Appointment.identifier.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1570,11 +1591,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.66796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.35546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2537,11 +2558,11 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -2556,17 +2577,15 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>131</v>
-      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
         <v>73</v>
@@ -2603,16 +2622,14 @@
         <v>73</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AB9" s="2"/>
       <c r="AC9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AE9" t="s" s="2">
         <v>132</v>
@@ -2633,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2645,45 +2662,43 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
       <c r="O10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2731,7 +2746,7 @@
         <v>73</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>74</v>
@@ -2740,7 +2755,7 @@
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>133</v>
@@ -2749,7 +2764,7 @@
         <v>73</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2763,9 +2778,11 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="C11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2783,16 +2800,16 @@
         <v>73</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -2843,7 +2860,7 @@
         <v>73</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>74</v>
@@ -2852,62 +2869,66 @@
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O12" t="s" s="2">
         <v>73</v>
       </c>
@@ -2955,25 +2976,25 @@
         <v>73</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2985,42 +3006,40 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
         <v>73</v>
@@ -3057,19 +3076,19 @@
         <v>73</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="AC13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>74</v>
@@ -3081,27 +3100,27 @@
         <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AN13" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3118,26 +3137,22 @@
         <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
         <v>73</v>
       </c>
@@ -3161,13 +3176,13 @@
         <v>73</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>73</v>
@@ -3185,7 +3200,7 @@
         <v>73</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>74</v>
@@ -3197,13 +3212,13 @@
         <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3212,23 +3227,23 @@
         <v>73</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>125</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>73</v>
@@ -3237,23 +3252,21 @@
         <v>73</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
         <v>73</v>
       </c>
@@ -3277,49 +3290,49 @@
         <v>73</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3328,12 +3341,12 @@
         <v>73</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3341,34 +3354,34 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>73</v>
@@ -3381,7 +3394,7 @@
         <v>73</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>73</v>
@@ -3393,13 +3406,13 @@
         <v>73</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>73</v>
@@ -3417,7 +3430,7 @@
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>74</v>
@@ -3435,7 +3448,7 @@
         <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>73</v>
@@ -3444,12 +3457,12 @@
         <v>73</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3457,13 +3470,13 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -3472,18 +3485,20 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O17" t="s" s="2">
         <v>73</v>
       </c>
@@ -3495,7 +3510,7 @@
         <v>73</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>73</v>
@@ -3507,13 +3522,13 @@
         <v>73</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -3531,7 +3546,7 @@
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>74</v>
@@ -3549,7 +3564,7 @@
         <v>73</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3558,12 +3573,12 @@
         <v>73</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3586,16 +3601,20 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="O18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3607,7 +3626,7 @@
         <v>73</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>73</v>
@@ -3643,7 +3662,7 @@
         <v>73</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>74</v>
@@ -3661,7 +3680,7 @@
         <v>73</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
@@ -3670,12 +3689,12 @@
         <v>73</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3683,13 +3702,13 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -3698,16 +3717,16 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
@@ -3721,7 +3740,7 @@
         <v>73</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>73</v>
@@ -3757,7 +3776,7 @@
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>74</v>
@@ -3775,7 +3794,7 @@
         <v>73</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>73</v>
@@ -3784,12 +3803,12 @@
         <v>73</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3797,32 +3816,30 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
         <v>73</v>
@@ -3832,7 +3849,7 @@
         <v>73</v>
       </c>
       <c r="R20" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>73</v>
@@ -3847,13 +3864,13 @@
         <v>73</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>219</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -3871,10 +3888,10 @@
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -3886,24 +3903,24 @@
         <v>94</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>73</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3926,15 +3943,17 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>73</v>
@@ -3959,11 +3978,13 @@
         <v>73</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="X21" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Y21" t="s" s="2">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>73</v>
@@ -3981,7 +4002,7 @@
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>74</v>
@@ -3999,7 +4020,7 @@
         <v>73</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>153</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -4008,12 +4029,12 @@
         <v>73</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>73</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4021,30 +4042,32 @@
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>73</v>
@@ -4054,7 +4077,7 @@
         <v>73</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>73</v>
@@ -4069,11 +4092,13 @@
         <v>73</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="X22" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="Y22" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -4091,13 +4116,13 @@
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>73</v>
@@ -4106,24 +4131,24 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>73</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>73</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4134,7 +4159,7 @@
         <v>74</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>73</v>
@@ -4146,17 +4171,15 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>73</v>
@@ -4181,11 +4204,11 @@
         <v>73</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="X23" s="2"/>
       <c r="Y23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>73</v>
@@ -4203,13 +4226,13 @@
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>73</v>
@@ -4218,10 +4241,10 @@
         <v>94</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>241</v>
+        <v>73</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -4235,7 +4258,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4258,13 +4281,13 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4291,11 +4314,11 @@
         <v>73</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="X24" s="2"/>
       <c r="Y24" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -4313,7 +4336,7 @@
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>74</v>
@@ -4331,13 +4354,13 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>73</v>
@@ -4345,7 +4368,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4356,7 +4379,7 @@
         <v>74</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>73</v>
@@ -4368,15 +4391,17 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>73</v>
@@ -4401,11 +4426,11 @@
         <v>73</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="X25" s="2"/>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -4423,13 +4448,13 @@
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>73</v>
@@ -4438,24 +4463,24 @@
         <v>94</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>73</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>254</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4478,13 +4503,13 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4513,11 +4538,9 @@
       <c r="W26" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="X26" t="s" s="2">
-        <v>258</v>
-      </c>
+      <c r="X26" s="2"/>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -4535,7 +4558,7 @@
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4550,24 +4573,24 @@
         <v>94</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>260</v>
+        <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>73</v>
+        <v>253</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4578,7 +4601,7 @@
         <v>74</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>73</v>
@@ -4587,16 +4610,16 @@
         <v>73</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4623,13 +4646,11 @@
         <v>73</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="X27" s="2"/>
       <c r="Y27" t="s" s="2">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -4647,13 +4668,13 @@
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>73</v>
@@ -4662,24 +4683,24 @@
         <v>94</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>73</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4690,7 +4711,7 @@
         <v>74</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>73</v>
@@ -4699,20 +4720,18 @@
         <v>73</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>270</v>
+        <v>177</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>73</v>
@@ -4737,13 +4756,13 @@
         <v>73</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>73</v>
+        <v>264</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -4761,13 +4780,13 @@
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>73</v>
@@ -4776,24 +4795,24 @@
         <v>94</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4804,7 +4823,7 @@
         <v>74</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>73</v>
@@ -4816,13 +4835,13 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>149</v>
+        <v>270</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -4873,13 +4892,13 @@
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>73</v>
@@ -4888,24 +4907,24 @@
         <v>94</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
+        <v>273</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>73</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4916,7 +4935,7 @@
         <v>74</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>73</v>
@@ -4928,15 +4947,17 @@
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="M30" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>73</v>
@@ -4985,13 +5006,13 @@
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>73</v>
@@ -5000,24 +5021,24 @@
         <v>94</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>73</v>
+        <v>283</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5025,28 +5046,28 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>293</v>
+        <v>156</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5097,7 +5118,7 @@
         <v>73</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>74</v>
@@ -5112,24 +5133,24 @@
         <v>94</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>73</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5140,7 +5161,7 @@
         <v>74</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>73</v>
@@ -5149,16 +5170,16 @@
         <v>73</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5209,13 +5230,13 @@
         <v>73</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>73</v>
@@ -5224,24 +5245,24 @@
         <v>94</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>307</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5255,22 +5276,22 @@
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5321,7 +5342,7 @@
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5336,24 +5357,24 @@
         <v>94</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>73</v>
+        <v>305</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>73</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5364,7 +5385,7 @@
         <v>74</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>73</v>
@@ -5373,16 +5394,16 @@
         <v>73</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -5433,13 +5454,13 @@
         <v>73</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>73</v>
@@ -5448,24 +5469,24 @@
         <v>94</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>73</v>
+        <v>302</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>73</v>
+        <v>311</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>73</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5488,17 +5509,15 @@
         <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>73</v>
@@ -5547,7 +5566,7 @@
         <v>73</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>74</v>
@@ -5562,13 +5581,13 @@
         <v>94</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>73</v>
@@ -5579,7 +5598,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5590,7 +5609,7 @@
         <v>74</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>73</v>
@@ -5602,17 +5621,15 @@
         <v>73</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>149</v>
+        <v>321</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>73</v>
@@ -5661,13 +5678,13 @@
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>73</v>
@@ -5676,24 +5693,24 @@
         <v>94</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>331</v>
+        <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>333</v>
+        <v>73</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5716,15 +5733,17 @@
         <v>73</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>149</v>
+        <v>326</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>73</v>
@@ -5773,7 +5792,7 @@
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -5788,35 +5807,35 @@
         <v>94</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AM37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>339</v>
+        <v>73</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>73</v>
@@ -5828,15 +5847,17 @@
         <v>73</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>340</v>
+        <v>156</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M38" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
         <v>73</v>
@@ -5885,13 +5906,13 @@
         <v>73</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>73</v>
@@ -5900,24 +5921,24 @@
         <v>94</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>73</v>
+        <v>339</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>73</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5925,11 +5946,11 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="F39" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="G39" t="s" s="2">
         <v>73</v>
       </c>
@@ -5940,13 +5961,13 @@
         <v>73</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>346</v>
+        <v>156</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -5997,53 +6018,53 @@
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AH39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>349</v>
+        <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>350</v>
+        <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>353</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -6052,13 +6073,13 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>149</v>
+        <v>346</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>150</v>
+        <v>347</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>151</v>
+        <v>348</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6109,25 +6130,25 @@
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>152</v>
+        <v>344</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>73</v>
+        <v>349</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>153</v>
+        <v>350</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6141,15 +6162,15 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>75</v>
@@ -6164,17 +6185,15 @@
         <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>128</v>
+        <v>352</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>129</v>
+        <v>353</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
         <v>73</v>
@@ -6223,10 +6242,10 @@
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>159</v>
+        <v>351</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6235,63 +6254,59 @@
         <v>73</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>133</v>
+        <v>355</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>73</v>
+        <v>356</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>153</v>
+        <v>357</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>73</v>
+        <v>358</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>73</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
-        <v>357</v>
+        <v>73</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>358</v>
+        <v>157</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>73</v>
       </c>
@@ -6339,25 +6354,25 @@
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>360</v>
+        <v>159</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6375,7 +6390,7 @@
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6391,19 +6406,19 @@
         <v>73</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>362</v>
+        <v>162</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
+        <v>143</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -6429,13 +6444,13 @@
         <v>73</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>365</v>
+        <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>73</v>
@@ -6453,7 +6468,7 @@
         <v>73</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>74</v>
@@ -6465,59 +6480,63 @@
         <v>73</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>367</v>
+        <v>160</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>368</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
-        <v>73</v>
+        <v>363</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>370</v>
+        <v>127</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O44" t="s" s="2">
         <v>73</v>
       </c>
@@ -6565,39 +6584,39 @@
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>373</v>
+        <v>125</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>374</v>
+        <v>73</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>375</v>
+        <v>73</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>376</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6608,7 +6627,7 @@
         <v>74</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>73</v>
@@ -6620,15 +6639,17 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M45" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>73</v>
@@ -6653,13 +6674,13 @@
         <v>73</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>73</v>
@@ -6677,13 +6698,13 @@
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>73</v>
@@ -6695,21 +6716,21 @@
         <v>73</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>383</v>
+        <v>160</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>73</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6717,7 +6738,7 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>82</v>
@@ -6732,13 +6753,13 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>102</v>
+        <v>376</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6765,13 +6786,13 @@
         <v>73</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>387</v>
+        <v>73</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>388</v>
+        <v>73</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>73</v>
@@ -6789,10 +6810,10 @@
         <v>73</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -6807,21 +6828,21 @@
         <v>73</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>73</v>
+        <v>381</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -6841,16 +6862,16 @@
         <v>73</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6877,13 +6898,13 @@
         <v>73</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>73</v>
+        <v>386</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>73</v>
+        <v>387</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>73</v>
@@ -6901,7 +6922,7 @@
         <v>73</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
@@ -6919,10 +6940,10 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>153</v>
+        <v>388</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>73</v>
+        <v>389</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>73</v>
@@ -6933,7 +6954,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -6941,10 +6962,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>73</v>
@@ -6953,20 +6974,18 @@
         <v>73</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>73</v>
@@ -6991,13 +7010,13 @@
         <v>73</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>73</v>
+        <v>393</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>73</v>
+        <v>394</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>73</v>
@@ -7015,13 +7034,13 @@
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>73</v>
@@ -7030,23 +7049,249 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="L49" t="s" s="2">
         <v>400</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="P50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN48">
+  <autoFilter ref="A1:AN50">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7056,7 +7301,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
